--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6285B6A-17E6-48A4-B292-E8D6D15BC529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F550FE03-A3D9-4E10-A565-8AFD21889B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EC49D552-B348-4815-9BAC-C35C6B92658A}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
-    <sheet name="3" sheetId="2" r:id="rId2"/>
+    <sheet name="4" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1'!$A$1:$D$113</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3'!$A$1:$D$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'4'!$A$1:$D$176</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'3'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'4'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F550FE03-A3D9-4E10-A565-8AFD21889B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF12E356-D23D-447F-ADA1-DAB70FBFFC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EC49D552-B348-4815-9BAC-C35C6B92658A}"/>
   </bookViews>
@@ -607,9 +607,6 @@
     <t>40019042401</t>
   </si>
   <si>
-    <t>TRAJE NIÑO 12 G47815-17 + CHAL</t>
-  </si>
-  <si>
     <t>40020072404</t>
   </si>
   <si>
@@ -1313,6 +1310,9 @@
   </si>
   <si>
     <t>SE AGREGO AL FINAL</t>
+  </si>
+  <si>
+    <t>TRAJE NIÑO G47815-17 + CHAL</t>
   </si>
 </sst>
 </file>
@@ -3205,10 +3205,10 @@
         <v>6</v>
       </c>
       <c r="E1" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>243</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="E2" s="33"/>
       <c r="F2" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3260,35 +3260,35 @@
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
       <c r="A5" s="35"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D5" s="37">
         <v>1</v>
       </c>
       <c r="E5" s="33"/>
       <c r="F5" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
       <c r="A6" s="35"/>
       <c r="B6" s="36"/>
       <c r="C6" s="36" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D6" s="37">
         <v>1</v>
       </c>
       <c r="E6" s="33"/>
       <c r="F6" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3296,38 +3296,38 @@
         <v>128</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D7" s="37">
         <v>1</v>
       </c>
       <c r="E7" s="33"/>
       <c r="F7" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18.75" customHeight="1">
       <c r="A8" s="30"/>
       <c r="B8" s="31"/>
       <c r="C8" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D8" s="32">
         <v>3</v>
       </c>
       <c r="E8" s="33"/>
       <c r="F8" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1">
       <c r="A9" s="12"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" s="20">
         <v>2</v>
@@ -3339,21 +3339,21 @@
       <c r="A10" s="38"/>
       <c r="B10" s="39"/>
       <c r="C10" s="39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D10" s="40">
         <v>5</v>
       </c>
       <c r="E10" s="33"/>
       <c r="F10" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18.75" customHeight="1">
       <c r="A11" s="12"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D11" s="20">
         <v>4</v>
@@ -3365,7 +3365,7 @@
       <c r="A12" s="12"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D12" s="20">
         <v>19</v>
@@ -3377,7 +3377,7 @@
       <c r="A13" s="12"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D13" s="20">
         <v>7</v>
@@ -3389,7 +3389,7 @@
       <c r="A14" s="12"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D14" s="20">
         <v>5</v>
@@ -3401,7 +3401,7 @@
       <c r="A15" s="12"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D15" s="20">
         <v>5</v>
@@ -3413,7 +3413,7 @@
       <c r="A16" s="12"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D16" s="20">
         <v>8</v>
@@ -3425,7 +3425,7 @@
       <c r="A17" s="12"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D17" s="20">
         <v>2</v>
@@ -3437,7 +3437,7 @@
       <c r="A18" s="12"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D18" s="20">
         <v>2</v>
@@ -3449,7 +3449,7 @@
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D19" s="19">
         <v>4</v>
@@ -3465,14 +3465,14 @@
         <v>129</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D20" s="37">
         <v>1</v>
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3480,17 +3480,17 @@
         <v>3</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D21" s="37">
         <v>1</v>
       </c>
       <c r="E21" s="33"/>
       <c r="F21" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3498,17 +3498,17 @@
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D22" s="37">
         <v>1</v>
       </c>
       <c r="E22" s="33"/>
       <c r="F22" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3516,17 +3516,17 @@
         <v>3</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D23" s="37">
         <v>1</v>
       </c>
       <c r="E23" s="33"/>
       <c r="F23" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3534,17 +3534,17 @@
         <v>3</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D24" s="37">
         <v>1</v>
       </c>
       <c r="E24" s="33"/>
       <c r="F24" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3552,24 +3552,24 @@
         <v>3</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D25" s="37">
         <v>1</v>
       </c>
       <c r="E25" s="33"/>
       <c r="F25" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D26" s="21">
         <v>1</v>
@@ -3581,28 +3581,28 @@
       <c r="A27" s="41"/>
       <c r="B27" s="42"/>
       <c r="C27" s="42" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D27" s="43">
         <v>1</v>
       </c>
       <c r="E27" s="33"/>
       <c r="F27" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
       <c r="A28" s="35"/>
       <c r="B28" s="36"/>
       <c r="C28" s="36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" s="37">
         <v>19</v>
       </c>
       <c r="E28" s="33"/>
       <c r="F28" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="E30" s="33"/>
       <c r="F30" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1">
@@ -3677,21 +3677,21 @@
       <c r="A33" s="30"/>
       <c r="B33" s="31"/>
       <c r="C33" s="31" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D33" s="32">
         <v>1</v>
       </c>
       <c r="E33" s="33"/>
       <c r="F33" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D34" s="19">
         <v>3</v>
@@ -3714,21 +3714,21 @@
       </c>
       <c r="E35" s="33"/>
       <c r="F35" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18.75" customHeight="1">
       <c r="A36" s="38"/>
       <c r="B36" s="39"/>
       <c r="C36" s="39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D36" s="40">
         <v>16</v>
       </c>
       <c r="E36" s="33"/>
       <c r="F36" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="18.75" customHeight="1">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="E39" s="33"/>
       <c r="F39" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="E40" s="33"/>
       <c r="F40" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E41" s="33"/>
       <c r="F41" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="24">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="E42" s="57"/>
       <c r="F42" s="58" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="36.75" thickBot="1">
@@ -3843,14 +3843,14 @@
         <v>30042015664</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D43" s="22">
         <v>2</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="59" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="E44" s="33"/>
       <c r="F44" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="E45" s="33"/>
       <c r="F45" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="18.75" customHeight="1">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="E46" s="33"/>
       <c r="F46" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3954,21 +3954,21 @@
       </c>
       <c r="E49" s="33"/>
       <c r="F49" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18.75" customHeight="1">
       <c r="A50" s="30"/>
       <c r="B50" s="31"/>
       <c r="C50" s="31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D50" s="32">
         <v>1</v>
       </c>
       <c r="E50" s="33"/>
       <c r="F50" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="42" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D51" s="43">
         <v>1</v>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="E52" s="33"/>
       <c r="F52" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="E53" s="33"/>
       <c r="F53" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="E54" s="33"/>
       <c r="F54" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -4044,17 +4044,17 @@
         <v>7</v>
       </c>
       <c r="B55" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="C55" s="36" t="s">
         <v>204</v>
-      </c>
-      <c r="C55" s="36" t="s">
-        <v>205</v>
       </c>
       <c r="D55" s="37">
         <v>1</v>
       </c>
       <c r="E55" s="33"/>
       <c r="F55" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="E56" s="33"/>
       <c r="F56" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -4083,14 +4083,14 @@
         <v>16</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D57" s="46">
         <v>1</v>
       </c>
       <c r="E57" s="33"/>
       <c r="F57" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="18.75" customHeight="1">
@@ -4101,14 +4101,14 @@
         <v>136</v>
       </c>
       <c r="C58" s="48" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D58" s="49">
         <v>1</v>
       </c>
       <c r="E58" s="50"/>
       <c r="F58" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="18.75" customHeight="1">
@@ -4119,7 +4119,7 @@
         <v>137</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D59" s="26">
         <v>1</v>
@@ -4135,7 +4135,7 @@
         <v>116</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D60" s="29">
         <v>1</v>
@@ -4151,35 +4151,35 @@
         <v>15</v>
       </c>
       <c r="C61" s="52" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D61" s="53">
         <v>1</v>
       </c>
       <c r="E61" s="33"/>
       <c r="F61" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="18.75" customHeight="1">
       <c r="A62" s="30"/>
       <c r="B62" s="31"/>
       <c r="C62" s="31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D62" s="32">
         <v>1</v>
       </c>
       <c r="E62" s="33"/>
       <c r="F62" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="18.75" customHeight="1">
       <c r="A63" s="12"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D63" s="20">
         <v>3</v>
@@ -4191,7 +4191,7 @@
       <c r="A64" s="12"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D64" s="20">
         <v>1</v>
@@ -4203,7 +4203,7 @@
       <c r="A65" s="12"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D65" s="20">
         <v>1</v>
@@ -4215,7 +4215,7 @@
       <c r="A66" s="12"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D66" s="20">
         <v>2</v>
@@ -4227,7 +4227,7 @@
       <c r="A67" s="12"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D67" s="20">
         <v>1</v>
@@ -4239,7 +4239,7 @@
       <c r="A68" s="12"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D68" s="20">
         <v>1</v>
@@ -4251,7 +4251,7 @@
       <c r="A69" s="12"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D69" s="20">
         <v>2</v>
@@ -4263,7 +4263,7 @@
       <c r="A70" s="12"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D70" s="20">
         <v>2</v>
@@ -4275,7 +4275,7 @@
       <c r="A71" s="12"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D71" s="20">
         <v>1</v>
@@ -4287,7 +4287,7 @@
       <c r="A72" s="12"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D72" s="20">
         <v>3</v>
@@ -4299,7 +4299,7 @@
       <c r="A73" s="12"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D73" s="20">
         <v>3</v>
@@ -4311,7 +4311,7 @@
       <c r="A74" s="8"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D74" s="19">
         <v>1</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="E75" s="33"/>
       <c r="F75" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" thickBot="1">
@@ -4358,17 +4358,17 @@
         <v>3</v>
       </c>
       <c r="B77" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="C77" s="36" t="s">
         <v>189</v>
-      </c>
-      <c r="C77" s="36" t="s">
-        <v>190</v>
       </c>
       <c r="D77" s="37">
         <v>1</v>
       </c>
       <c r="E77" s="33"/>
       <c r="F77" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" thickBot="1">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="E79" s="33"/>
       <c r="F79" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="16.5" thickBot="1">
@@ -4413,14 +4413,14 @@
         <v>132</v>
       </c>
       <c r="C80" s="36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D80" s="37">
         <v>1</v>
       </c>
       <c r="E80" s="33"/>
       <c r="F80" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" thickBot="1">
@@ -4431,7 +4431,7 @@
         <v>133</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D81" s="23">
         <v>1</v>
@@ -4447,14 +4447,14 @@
         <v>134</v>
       </c>
       <c r="C82" s="36" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D82" s="37">
         <v>1</v>
       </c>
       <c r="E82" s="33"/>
       <c r="F82" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="16.5" thickBot="1">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="E83" s="33"/>
       <c r="F83" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="16.5" thickBot="1">
@@ -4490,21 +4490,21 @@
       </c>
       <c r="E84" s="33"/>
       <c r="F84" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="16.5" thickBot="1">
       <c r="A85" s="35"/>
       <c r="B85" s="36"/>
       <c r="C85" s="36" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D85" s="37">
         <v>1</v>
       </c>
       <c r="E85" s="33"/>
       <c r="F85" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="16.5" thickBot="1">
@@ -4515,14 +4515,14 @@
         <v>144</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D86" s="37">
         <v>1</v>
       </c>
       <c r="E86" s="33"/>
       <c r="F86" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="16.5" thickBot="1">
@@ -4530,17 +4530,17 @@
         <v>3</v>
       </c>
       <c r="B87" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C87" s="36" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D87" s="37">
         <v>1</v>
       </c>
       <c r="E87" s="33"/>
       <c r="F87" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="16.5" thickBot="1">
@@ -4551,14 +4551,14 @@
         <v>135</v>
       </c>
       <c r="C88" s="36" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D88" s="37">
         <v>2</v>
       </c>
       <c r="E88" s="33"/>
       <c r="F88" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="16.5" thickBot="1">
@@ -4569,14 +4569,14 @@
         <v>142</v>
       </c>
       <c r="C89" s="36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D89" s="37">
         <v>1</v>
       </c>
       <c r="E89" s="33"/>
       <c r="F89" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="16.5" thickBot="1">
@@ -4587,14 +4587,14 @@
         <v>143</v>
       </c>
       <c r="C90" s="36" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D90" s="37">
         <v>2</v>
       </c>
       <c r="E90" s="33"/>
       <c r="F90" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75">
@@ -4605,14 +4605,14 @@
         <v>117</v>
       </c>
       <c r="C91" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D91" s="32">
         <v>3</v>
       </c>
       <c r="E91" s="33"/>
       <c r="F91" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" thickBot="1">
@@ -4623,7 +4623,7 @@
         <v>118</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D92" s="19">
         <v>1</v>
@@ -4639,14 +4639,14 @@
         <v>119</v>
       </c>
       <c r="C93" s="36" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D93" s="37">
         <v>1</v>
       </c>
       <c r="E93" s="33"/>
       <c r="F93" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75">
@@ -4657,14 +4657,14 @@
         <v>140</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D94" s="32">
         <v>1</v>
       </c>
       <c r="E94" s="33"/>
       <c r="F94" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1">
@@ -4675,7 +4675,7 @@
         <v>141</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D95" s="19">
         <v>2</v>
@@ -4691,14 +4691,14 @@
         <v>120</v>
       </c>
       <c r="C96" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D96" s="32">
         <v>2</v>
       </c>
       <c r="E96" s="33"/>
       <c r="F96" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" thickBot="1">
@@ -4709,7 +4709,7 @@
         <v>121</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D97" s="19">
         <v>1</v>
@@ -4721,14 +4721,14 @@
       <c r="A98" s="35"/>
       <c r="B98" s="36"/>
       <c r="C98" s="36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D98" s="37">
         <v>1</v>
       </c>
       <c r="E98" s="33"/>
       <c r="F98" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="16.5" thickBot="1">
@@ -4739,14 +4739,14 @@
         <v>149</v>
       </c>
       <c r="C99" s="36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D99" s="37">
         <v>1</v>
       </c>
       <c r="E99" s="33"/>
       <c r="F99" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="16.5" thickBot="1">
@@ -4757,14 +4757,14 @@
         <v>18</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D100" s="37">
         <v>1</v>
       </c>
       <c r="E100" s="33"/>
       <c r="F100" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.75">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="E101" s="33"/>
       <c r="F101" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="15.75" thickBot="1">
@@ -4790,10 +4790,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D102" s="19">
         <v>1</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="E103" s="33"/>
       <c r="F103" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="16.5" thickBot="1">
@@ -4827,14 +4827,14 @@
         <v>17</v>
       </c>
       <c r="C104" s="36" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D104" s="37">
         <v>1</v>
       </c>
       <c r="E104" s="33"/>
       <c r="F104" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.75">
@@ -4845,21 +4845,21 @@
         <v>113</v>
       </c>
       <c r="C105" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D105" s="32">
         <v>1</v>
       </c>
       <c r="E105" s="33"/>
       <c r="F105" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15">
       <c r="A106" s="12"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D106" s="20">
         <v>2</v>
@@ -4875,7 +4875,7 @@
         <v>115</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D107" s="20">
         <v>3</v>
@@ -4887,7 +4887,7 @@
       <c r="A108" s="8"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D108" s="19">
         <v>1</v>
@@ -4903,14 +4903,14 @@
         <v>114</v>
       </c>
       <c r="C109" s="36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D109" s="37">
         <v>1</v>
       </c>
       <c r="E109" s="33"/>
       <c r="F109" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="16.5" thickBot="1">
@@ -4928,21 +4928,21 @@
       </c>
       <c r="E110" s="33"/>
       <c r="F110" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="16.5" thickBot="1">
       <c r="A111" s="35"/>
       <c r="B111" s="36"/>
       <c r="C111" s="36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D111" s="37">
         <v>1</v>
       </c>
       <c r="E111" s="33"/>
       <c r="F111" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="16.5" thickBot="1">
@@ -4950,17 +4950,17 @@
         <v>3</v>
       </c>
       <c r="B112" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C112" s="36" t="s">
         <v>199</v>
-      </c>
-      <c r="C112" s="36" t="s">
-        <v>200</v>
       </c>
       <c r="D112" s="37">
         <v>1</v>
       </c>
       <c r="E112" s="33"/>
       <c r="F112" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="16.5" thickBot="1">
@@ -4968,17 +4968,17 @@
         <v>3</v>
       </c>
       <c r="B113" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="C113" s="36" t="s">
         <v>191</v>
-      </c>
-      <c r="C113" s="36" t="s">
-        <v>192</v>
       </c>
       <c r="D113" s="37">
         <v>1</v>
       </c>
       <c r="E113" s="33"/>
       <c r="F113" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="16.5" thickBot="1">
@@ -4987,14 +4987,14 @@
       </c>
       <c r="B114" s="157"/>
       <c r="C114" s="157" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D114" s="158">
         <v>1</v>
       </c>
       <c r="E114" s="159"/>
       <c r="F114" s="160" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="16.5" thickBot="1">
@@ -5003,14 +5003,14 @@
       </c>
       <c r="B115" s="157"/>
       <c r="C115" s="157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D115" s="158">
         <v>1</v>
       </c>
       <c r="E115" s="159"/>
       <c r="F115" s="160" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="15.75" thickBot="1">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="B116" s="11"/>
       <c r="C116" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D116" s="64">
         <v>1</v>
@@ -5098,13 +5098,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E1" s="62" t="s">
+        <v>242</v>
+      </c>
+      <c r="F1" s="63" t="s">
         <v>243</v>
-      </c>
-      <c r="F1" s="63" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" thickBot="1">
@@ -5128,10 +5128,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>202</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>203</v>
       </c>
       <c r="D3" s="65">
         <v>1</v>
@@ -5465,14 +5465,14 @@
       </c>
       <c r="B24" s="72"/>
       <c r="C24" s="72" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D24" s="73">
         <v>0</v>
       </c>
       <c r="E24" s="74"/>
       <c r="F24" s="120" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="60.75" thickBot="1">
@@ -5481,14 +5481,14 @@
       </c>
       <c r="B25" s="72"/>
       <c r="C25" s="72" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D25" s="73">
         <v>0</v>
       </c>
       <c r="E25" s="74"/>
       <c r="F25" s="120" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="60.75" thickBot="1">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="B26" s="72"/>
       <c r="C26" s="72" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D26" s="73">
         <v>0</v>
       </c>
       <c r="E26" s="74"/>
       <c r="F26" s="120" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="B27" s="88"/>
       <c r="C27" s="93" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D27" s="99">
         <v>1</v>
@@ -5525,7 +5525,7 @@
       <c r="A28" s="85"/>
       <c r="B28" s="88"/>
       <c r="C28" s="93" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D28" s="99">
         <v>1</v>
@@ -5537,7 +5537,7 @@
       <c r="A29" s="85"/>
       <c r="B29" s="136"/>
       <c r="C29" s="78" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D29" s="137">
         <v>1</v>
@@ -5549,7 +5549,7 @@
       <c r="A30" s="138"/>
       <c r="B30" s="123"/>
       <c r="C30" s="124" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D30" s="125">
         <v>1</v>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="B31" s="25"/>
       <c r="C31" s="80" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D31" s="113">
         <v>1</v>
@@ -5575,7 +5575,7 @@
       <c r="A32" s="121"/>
       <c r="B32" s="25"/>
       <c r="C32" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D32" s="113">
         <v>4</v>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="80" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D33" s="113">
         <v>2</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="80" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D34" s="113">
         <v>1</v>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="80" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D35" s="113">
         <v>2</v>
@@ -5629,7 +5629,7 @@
       <c r="A36" s="138"/>
       <c r="B36" s="111"/>
       <c r="C36" s="91" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D36" s="112">
         <v>1</v>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D37" s="113">
         <v>1</v>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D38" s="113">
         <v>1</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B39" s="123"/>
       <c r="C39" s="124" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D39" s="125">
         <v>1</v>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="B40" s="25"/>
       <c r="C40" s="80" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D40" s="113">
         <v>2</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="B41" s="111"/>
       <c r="C41" s="91" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D41" s="112">
         <v>1</v>
@@ -5711,7 +5711,7 @@
       <c r="A42" s="105"/>
       <c r="B42" s="25"/>
       <c r="C42" s="80" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D42" s="113">
         <v>1</v>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B43" s="111"/>
       <c r="C43" s="91" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D43" s="112">
         <v>1</v>
@@ -5737,7 +5737,7 @@
       <c r="A44" s="138"/>
       <c r="B44" s="126"/>
       <c r="C44" s="127" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D44" s="128">
         <v>1</v>
@@ -5749,7 +5749,7 @@
       <c r="A45" s="110"/>
       <c r="B45" s="76"/>
       <c r="C45" s="76" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D45" s="77">
         <v>13</v>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D46" s="70">
         <v>2</v>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D47" s="70">
         <v>4</v>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D48" s="70">
         <v>4</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D49" s="70">
         <v>1</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D50" s="70">
         <v>2</v>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D51" s="70">
         <v>1</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D52" s="70">
         <v>1</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D53" s="70">
         <v>2</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D54" s="70">
         <v>2</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D55" s="70">
         <v>1</v>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B56" s="87"/>
       <c r="C56" s="92" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D56" s="98">
         <v>1</v>
@@ -5915,7 +5915,7 @@
       <c r="A57" s="84"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D57" s="70">
         <v>2</v>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="B58" s="108"/>
       <c r="C58" s="108" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D58" s="118">
         <v>1</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="B59" s="111"/>
       <c r="C59" s="91" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D59" s="97">
         <v>2</v>
@@ -5955,7 +5955,7 @@
       <c r="A60" s="150"/>
       <c r="B60" s="111"/>
       <c r="C60" s="91" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D60" s="97">
         <v>1</v>
@@ -5967,7 +5967,7 @@
       <c r="A61" s="105"/>
       <c r="B61" s="25"/>
       <c r="C61" s="80" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D61" s="81">
         <v>1</v>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="B62" s="111"/>
       <c r="C62" s="91" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D62" s="97">
         <v>1</v>
@@ -5993,7 +5993,7 @@
       <c r="A63" s="107"/>
       <c r="B63" s="111"/>
       <c r="C63" s="91" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D63" s="97">
         <v>1</v>
@@ -6005,7 +6005,7 @@
       <c r="A64" s="107"/>
       <c r="B64" s="111"/>
       <c r="C64" s="91" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D64" s="97">
         <v>4</v>
@@ -6017,7 +6017,7 @@
       <c r="A65" s="107"/>
       <c r="B65" s="114"/>
       <c r="C65" s="96" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D65" s="102">
         <v>3</v>
@@ -6029,7 +6029,7 @@
       <c r="A66" s="107"/>
       <c r="B66" s="115"/>
       <c r="C66" s="92" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D66" s="98">
         <v>1</v>
@@ -6041,7 +6041,7 @@
       <c r="A67" s="107"/>
       <c r="B67" s="116"/>
       <c r="C67" s="117" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D67" s="119">
         <v>1</v>
@@ -6053,7 +6053,7 @@
       <c r="A68" s="110"/>
       <c r="B68" s="104"/>
       <c r="C68" s="96" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D68" s="102">
         <v>1</v>
@@ -6065,7 +6065,7 @@
       <c r="A69" s="83"/>
       <c r="B69" s="90"/>
       <c r="C69" s="95" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D69" s="101">
         <v>1</v>
@@ -6077,7 +6077,7 @@
       <c r="A70" s="86"/>
       <c r="B70" s="89"/>
       <c r="C70" s="94" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D70" s="100">
         <v>1</v>
@@ -6089,7 +6089,7 @@
       <c r="A71" s="83"/>
       <c r="B71" s="87"/>
       <c r="C71" s="92" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D71" s="98">
         <v>1</v>
@@ -6101,7 +6101,7 @@
       <c r="A72" s="84"/>
       <c r="B72" s="87"/>
       <c r="C72" s="92" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D72" s="98">
         <v>1</v>
@@ -6113,7 +6113,7 @@
       <c r="A73" s="84"/>
       <c r="B73" s="90"/>
       <c r="C73" s="95" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D73" s="101">
         <v>1</v>
@@ -6125,7 +6125,7 @@
       <c r="A74" s="86"/>
       <c r="B74" s="89"/>
       <c r="C74" s="94" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D74" s="100">
         <v>2</v>
@@ -6137,7 +6137,7 @@
       <c r="A75" s="83"/>
       <c r="B75" s="87"/>
       <c r="C75" s="92" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D75" s="98">
         <v>1</v>
@@ -6149,7 +6149,7 @@
       <c r="A76" s="84"/>
       <c r="B76" s="90"/>
       <c r="C76" s="95" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D76" s="101">
         <v>1</v>
@@ -6161,7 +6161,7 @@
       <c r="A77" s="86"/>
       <c r="B77" s="88"/>
       <c r="C77" s="93" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D77" s="99">
         <v>1</v>
@@ -6173,14 +6173,14 @@
       <c r="A78" s="85"/>
       <c r="B78" s="11"/>
       <c r="C78" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D78" s="64">
         <v>1</v>
       </c>
       <c r="E78" s="60"/>
       <c r="F78" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" thickBot="1">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="B79" s="11"/>
       <c r="C79" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D79" s="64">
         <v>1</v>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B80" s="72"/>
       <c r="C80" s="72" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D80" s="73">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="75" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" thickBot="1">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="B81" s="88"/>
       <c r="C81" s="93" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D81" s="99">
         <v>1</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="B83" s="143"/>
       <c r="C83" s="146" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D83" s="147">
         <v>1</v>
@@ -6261,7 +6261,7 @@
       <c r="A84" s="83"/>
       <c r="B84" s="144"/>
       <c r="C84" s="148" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D84" s="112">
         <v>2</v>
@@ -6273,7 +6273,7 @@
       <c r="A85" s="84"/>
       <c r="B85" s="145"/>
       <c r="C85" s="148" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D85" s="112">
         <v>1</v>
@@ -6285,21 +6285,21 @@
       <c r="A86" s="142"/>
       <c r="B86" s="149"/>
       <c r="C86" s="148" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D86" s="97">
         <v>1</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15.75" thickBot="1">
       <c r="A87" s="86"/>
       <c r="B87" s="89"/>
       <c r="C87" s="96" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D87" s="102">
         <v>1</v>
@@ -6311,7 +6311,7 @@
       <c r="A88" s="83"/>
       <c r="B88" s="87"/>
       <c r="C88" s="92" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D88" s="98">
         <v>1</v>
@@ -6323,7 +6323,7 @@
       <c r="A89" s="84"/>
       <c r="B89" s="90"/>
       <c r="C89" s="95" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D89" s="101">
         <v>1</v>
@@ -6335,7 +6335,7 @@
       <c r="A90" s="86"/>
       <c r="B90" s="88"/>
       <c r="C90" s="93" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D90" s="99">
         <v>1</v>
@@ -6347,7 +6347,7 @@
       <c r="A91" s="85"/>
       <c r="B91" s="11"/>
       <c r="C91" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D91" s="64">
         <v>1</v>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="B92" s="88"/>
       <c r="C92" s="93" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D92" s="99">
         <v>1</v>
@@ -6373,7 +6373,7 @@
       <c r="A93" s="85"/>
       <c r="B93" s="11"/>
       <c r="C93" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D93" s="64">
         <v>1</v>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B94" s="11"/>
       <c r="C94" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D94" s="64">
         <v>1</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="B95" s="11"/>
       <c r="C95" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D95" s="64">
         <v>1</v>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="B96" s="11"/>
       <c r="C96" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D96" s="64">
         <v>1</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="B97" s="11"/>
       <c r="C97" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D97" s="64">
         <v>1</v>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="B98" s="88"/>
       <c r="C98" s="93" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D98" s="99">
         <v>2</v>
@@ -6455,7 +6455,7 @@
       <c r="A99" s="85"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D99" s="69">
         <v>1</v>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="B100" s="9"/>
       <c r="C100" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D100" s="71">
         <v>2</v>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B101" s="89"/>
       <c r="C101" s="94" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D101" s="100">
         <v>1</v>
@@ -6495,7 +6495,7 @@
       <c r="A102" s="83"/>
       <c r="B102" s="87"/>
       <c r="C102" s="92" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D102" s="98">
         <v>1</v>
@@ -6507,7 +6507,7 @@
       <c r="A103" s="84"/>
       <c r="B103" s="87"/>
       <c r="C103" s="92" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D103" s="98">
         <v>1</v>
@@ -6519,7 +6519,7 @@
       <c r="A104" s="84"/>
       <c r="B104" s="87"/>
       <c r="C104" s="92" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D104" s="98">
         <v>3</v>
@@ -6531,7 +6531,7 @@
       <c r="A105" s="84"/>
       <c r="B105" s="87"/>
       <c r="C105" s="92" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D105" s="98">
         <v>4</v>
@@ -6543,7 +6543,7 @@
       <c r="A106" s="84"/>
       <c r="B106" s="90"/>
       <c r="C106" s="95" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D106" s="101">
         <v>1</v>
@@ -6555,7 +6555,7 @@
       <c r="A107" s="86"/>
       <c r="B107" s="139"/>
       <c r="C107" s="139" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D107" s="153">
         <v>1</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B108" s="154"/>
       <c r="C108" s="155" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D108" s="147">
         <v>1</v>
@@ -6581,7 +6581,7 @@
       <c r="A109" s="105"/>
       <c r="B109" s="111"/>
       <c r="C109" s="91" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D109" s="112">
         <v>2</v>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="B110" s="27"/>
       <c r="C110" s="28" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D110" s="135">
         <v>1</v>
@@ -6607,7 +6607,7 @@
       <c r="A111" s="86"/>
       <c r="B111" s="76"/>
       <c r="C111" s="76" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D111" s="77">
         <v>1</v>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="B112" s="87"/>
       <c r="C112" s="92" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D112" s="98">
         <v>1</v>
@@ -6633,7 +6633,7 @@
       <c r="A113" s="84"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D113" s="70">
         <v>3</v>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B114" s="9"/>
       <c r="C114" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D114" s="71">
         <v>1</v>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="B115" s="7"/>
       <c r="C115" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D115" s="69">
         <v>1</v>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B116" s="5"/>
       <c r="C116" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D116" s="70">
         <v>1</v>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D117" s="70">
         <v>7</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D118" s="70">
         <v>10</v>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D119" s="70">
         <v>6</v>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D120" s="70">
         <v>11</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D121" s="70">
         <v>1</v>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="B122" s="5"/>
       <c r="C122" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D122" s="70">
         <v>4</v>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D123" s="70">
         <v>2</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D124" s="70">
         <v>1</v>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="B125" s="90"/>
       <c r="C125" s="95" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D125" s="101">
         <v>1</v>
@@ -6813,7 +6813,7 @@
       <c r="A126" s="86"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D126" s="69">
         <v>1</v>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="B127" s="9"/>
       <c r="C127" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D127" s="71">
         <v>1</v>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="B128" s="88"/>
       <c r="C128" s="93" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D128" s="99">
         <v>1</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="B141" s="126"/>
       <c r="C141" s="127" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D141" s="128">
         <v>1</v>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="B147" s="27"/>
       <c r="C147" s="28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D147" s="135">
         <v>1</v>
@@ -7201,7 +7201,7 @@
         <v>89</v>
       </c>
       <c r="C151" s="124" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D151" s="134">
         <v>1</v>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B152" s="111"/>
       <c r="C152" s="91" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D152" s="112">
         <v>1</v>
@@ -7229,7 +7229,7 @@
         <v>90</v>
       </c>
       <c r="C153" s="28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D153" s="29">
         <v>2</v>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="B154" s="129"/>
       <c r="C154" s="129" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D154" s="130">
         <v>2</v>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="B155" s="88"/>
       <c r="C155" s="93" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D155" s="99">
         <v>1</v>
@@ -7269,7 +7269,7 @@
       <c r="A156" s="85"/>
       <c r="B156" s="88"/>
       <c r="C156" s="93" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D156" s="99">
         <v>1</v>
@@ -7281,7 +7281,7 @@
       <c r="A157" s="85"/>
       <c r="B157" s="88"/>
       <c r="C157" s="93" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D157" s="99">
         <v>1</v>
@@ -7293,7 +7293,7 @@
       <c r="A158" s="85"/>
       <c r="B158" s="89"/>
       <c r="C158" s="94" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D158" s="100">
         <v>1</v>
@@ -7305,7 +7305,7 @@
       <c r="A159" s="83"/>
       <c r="B159" s="87"/>
       <c r="C159" s="92" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D159" s="98">
         <v>1</v>
@@ -7317,7 +7317,7 @@
       <c r="A160" s="84"/>
       <c r="B160" s="90"/>
       <c r="C160" s="95" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D160" s="101">
         <v>1</v>
@@ -7329,7 +7329,7 @@
       <c r="A161" s="86"/>
       <c r="B161" s="88"/>
       <c r="C161" s="93" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D161" s="99">
         <v>1</v>
@@ -7341,7 +7341,7 @@
       <c r="A162" s="85"/>
       <c r="B162" s="11"/>
       <c r="C162" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D162" s="64">
         <v>1</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="B163" s="89"/>
       <c r="C163" s="94" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D163" s="100">
         <v>1</v>
@@ -7367,7 +7367,7 @@
       <c r="A164" s="83"/>
       <c r="B164" s="90"/>
       <c r="C164" s="95" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D164" s="101">
         <v>1</v>
@@ -7379,7 +7379,7 @@
       <c r="A165" s="86"/>
       <c r="B165" s="88"/>
       <c r="C165" s="93" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D165" s="99">
         <v>1</v>
@@ -7391,7 +7391,7 @@
       <c r="A166" s="85"/>
       <c r="B166" s="11"/>
       <c r="C166" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D166" s="64">
         <v>1</v>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="B167" s="11"/>
       <c r="C167" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D167" s="64">
         <v>1</v>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="B168" s="11"/>
       <c r="C168" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D168" s="64">
         <v>1</v>
@@ -7431,7 +7431,7 @@
       <c r="A169" s="10"/>
       <c r="B169" s="11"/>
       <c r="C169" s="11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D169" s="64">
         <v>1</v>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="B170" s="11"/>
       <c r="C170" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D170" s="64">
         <v>1</v>
@@ -7461,7 +7461,7 @@
         <v>186</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>187</v>
+        <v>422</v>
       </c>
       <c r="D171" s="65">
         <v>1</v>
@@ -7489,7 +7489,7 @@
       <c r="A173" s="151"/>
       <c r="B173" s="152"/>
       <c r="C173" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D173" s="66">
         <v>3</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B174" s="90"/>
       <c r="C174" s="95" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D174" s="101">
         <v>4</v>
@@ -7517,7 +7517,7 @@
         <v>40005022314</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D175" s="65">
         <v>1</v>
